--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487839_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487839_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.4277</v>
+        <v>13.2196</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6683</v>
+        <v>13.4896</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2406</v>
+        <v>-0.27</v>
       </c>
       <c r="G2" t="n">
         <v>7.4236</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0211</v>
+        <v>0.8131</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7484</v>
+        <v>0.5696</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2728</v>
+        <v>0.2434</v>
       </c>
       <c r="V2" t="n">
         <v>3.1099</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.626</v>
+        <v>3.6729</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9827</v>
+        <v>6.6874</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6433</v>
+        <v>-3.0145</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1716</v>
+        <v>6.0047</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4713</v>
+        <v>3.1235</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2996</v>
+        <v>2.8812</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4861</v>
+        <v>8.1113</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5734</v>
+        <v>3.8096</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.08740000000000001</v>
+        <v>4.3017</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3144</v>
+        <v>-2.1067</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1022</v>
+        <v>-0.6861</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2123</v>
+        <v>-1.4206</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2081</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6812</v>
+        <v>0.1608</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5559</v>
+        <v>-0.1804</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1253</v>
+        <v>0.3413</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9813</v>
+        <v>0.421</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9813</v>
+        <v>2.9188</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.4978</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0164</v>
+        <v>3.5419</v>
       </c>
       <c r="E4" t="n">
-        <v>6.473</v>
+        <v>2.8692</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.4566</v>
+        <v>0.6727</v>
       </c>
       <c r="G4" t="n">
-        <v>6.0047</v>
+        <v>1.1716</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1235</v>
+        <v>1.4713</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8812</v>
+        <v>-0.2996</v>
       </c>
       <c r="J4" t="n">
-        <v>8.1113</v>
+        <v>1.4861</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8096</v>
+        <v>1.5734</v>
       </c>
       <c r="L4" t="n">
-        <v>4.3017</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1067</v>
+        <v>-0.3144</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6861</v>
+        <v>-0.1022</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4206</v>
+        <v>-0.2123</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.9137</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5044</v>
+        <v>0.5971</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3948</v>
+        <v>0.4425</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8991</v>
+        <v>0.1546</v>
       </c>
       <c r="V4" t="n">
-        <v>0.421</v>
+        <v>1.9813</v>
       </c>
       <c r="W4" t="n">
-        <v>2.9188</v>
+        <v>1.9813</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3138</v>
+        <v>1.7439</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2412</v>
+        <v>0.3483</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0726</v>
+        <v>1.3955</v>
       </c>
       <c r="G5" t="n">
         <v>2.3423</v>
@@ -844,13 +844,13 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6576</v>
+        <v>-0.2275</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6524</v>
+        <v>-0.5453</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0052</v>
+        <v>0.3178</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1627</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8423</v>
+        <v>0.1439</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0049</v>
+        <v>-0.0886</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8472</v>
+        <v>0.2325</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1581</v>
+        <v>0.0367</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9939</v>
+        <v>0.2857</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1642</v>
+        <v>-0.249</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6882</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1608</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5274</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4699</v>
+        <v>0.0367</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8331</v>
+        <v>0.2857</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6368</v>
+        <v>-0.249</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8489</v>
+        <v>-0.3091</v>
       </c>
       <c r="T6" t="n">
-        <v>1.034</v>
+        <v>-0.0886</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8149999999999999</v>
+        <v>-0.2205</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5271</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6899</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1627</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0367</v>
+        <v>-0.3775</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1957</v>
+        <v>-0.755</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2325</v>
+        <v>0.3775</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0367</v>
+        <v>-2.1581</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2857</v>
+        <v>-0.9939</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.249</v>
+        <v>-1.1642</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.6882</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.1608</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.5274</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0367</v>
+        <v>-1.4699</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2857</v>
+        <v>-0.8331</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.249</v>
+        <v>-0.6368</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4162</v>
+        <v>0.6291</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1957</v>
+        <v>0.2839</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2205</v>
+        <v>0.3452</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.5271</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6899</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1627</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7993</v>
+        <v>-2.0515</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7602</v>
+        <v>-2.1592</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0391</v>
+        <v>0.1077</v>
       </c>
       <c r="G8" t="n">
         <v>-2.8225</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7875</v>
+        <v>-0.0396</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8482</v>
+        <v>-0.2471</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0607</v>
+        <v>0.2075</v>
       </c>
       <c r="V8" t="n">
         <v>-0.23</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1076</v>
+        <v>-2.3789</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5798</v>
+        <v>-1.0859</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5278</v>
+        <v>-1.2929</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9993</v>
@@ -1156,13 +1156,13 @@
         <v>1.8731</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6511</v>
+        <v>0.0776</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2396</v>
+        <v>-0.7458</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5885</v>
+        <v>0.8234</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3303</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.7243</v>
+        <v>-2.9933</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1522</v>
+        <v>-1.5092</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5721</v>
+        <v>-1.4841</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0062</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3262</v>
+        <v>0.3167</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3294</v>
+        <v>-0.2414</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3975</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3334</v>
+        <v>-3.6443</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3046</v>
+        <v>-1.7035</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0288</v>
+        <v>-1.9407</v>
       </c>
       <c r="G11" t="n">
         <v>0.9236</v>
@@ -1312,13 +1312,13 @@
         <v>1.4568</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1124</v>
+        <v>-0.4233</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2396</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1273</v>
+        <v>0.2153</v>
       </c>
       <c r="V11" t="n">
         <v>-3.5203</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9907</v>
+        <v>-4.2429</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7622</v>
+        <v>-3.1612</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2285</v>
+        <v>-1.0817</v>
       </c>
       <c r="G12" t="n">
         <v>-2.5475</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7346</v>
+        <v>0.0132</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0033</v>
+        <v>0.5977</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7313</v>
+        <v>-0.5845</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.307599999999994</v>
+        <v>6.6338</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6056</v>
+        <v>12.9319</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.2979</v>
+        <v>-6.298</v>
       </c>
       <c r="G13" t="n">
         <v>7.368900000000002</v>
@@ -1447,7 +1447,7 @@
         <v>13.2902</v>
       </c>
       <c r="L13" t="n">
-        <v>6.2046</v>
+        <v>6.204599999999998</v>
       </c>
       <c r="M13" t="n">
         <v>-12.1261</v>
@@ -1468,16 +1468,16 @@
         <v>12.4871</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0405</v>
+        <v>1.3668</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5614999999999998</v>
+        <v>-0.2354000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6023</v>
+        <v>1.6021</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.061399999999999</v>
+        <v>-1.0614</v>
       </c>
       <c r="W13" t="n">
         <v>7.1998</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.344</v>
+        <v>5.7638</v>
       </c>
       <c r="E14" t="n">
-        <v>6.8814</v>
+        <v>7.0957</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5374</v>
+        <v>-1.3319</v>
       </c>
       <c r="G14" t="n">
         <v>1.9977</v>
@@ -1546,13 +1546,13 @@
         <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5807</v>
+        <v>-0.1608</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4757</v>
+        <v>-0.2614</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.105</v>
+        <v>0.1005</v>
       </c>
       <c r="V14" t="n">
         <v>2.6782</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7574</v>
+        <v>3.7662</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0147</v>
+        <v>3.229</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7427</v>
+        <v>0.5372</v>
       </c>
       <c r="G15" t="n">
         <v>2.8191</v>
@@ -1624,13 +1624,13 @@
         <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2297</v>
+        <v>0.2385</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5748</v>
+        <v>-0.3605</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8045</v>
+        <v>0.599</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1238</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.232</v>
+        <v>3.3201</v>
       </c>
       <c r="E16" t="n">
         <v>5.1727</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9407</v>
+        <v>-1.8526</v>
       </c>
       <c r="G16" t="n">
         <v>1.4837</v>
@@ -1702,13 +1702,13 @@
         <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7085</v>
+        <v>-0.6204</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0562</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6524</v>
+        <v>-0.5643</v>
       </c>
       <c r="V16" t="n">
         <v>0.5838</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0306</v>
+        <v>1.7821</v>
       </c>
       <c r="E17" t="n">
-        <v>4.31</v>
+        <v>4.7387</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.2795</v>
+        <v>-2.9565</v>
       </c>
       <c r="G17" t="n">
         <v>0.1815</v>
@@ -1780,13 +1780,13 @@
         <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.723</v>
+        <v>-0.9714</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9415</v>
+        <v>-0.5129</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7815</v>
+        <v>-0.4586</v>
       </c>
       <c r="V17" t="n">
         <v>2.5721</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0196</v>
+        <v>0.0489</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4149</v>
+        <v>-0.249</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6636</v>
+        <v>-0.5565</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2487</v>
+        <v>0.3075</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8310999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.09130000000000001</v>
+        <v>0.0745</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0124</v>
+        <v>0.1195</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1037</v>
+        <v>-0.045</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1168</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4703</v>
+        <v>-1.8109</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0145</v>
+        <v>-0.4431</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4558</v>
+        <v>-1.3678</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4393</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7202</v>
+        <v>0.3797</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6615</v>
+        <v>0.2329</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0587</v>
+        <v>0.1468</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7513</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.031</v>
+        <v>-3.0222</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1132</v>
+        <v>-0.8989</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9178</v>
+        <v>-2.1233</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0757</v>
@@ -2092,13 +2092,13 @@
         <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5004</v>
+        <v>-0.4916</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1619</v>
+        <v>0.0524</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3385</v>
+        <v>-0.544</v>
       </c>
       <c r="V21" t="n">
         <v>-1.7442</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9884</v>
+        <v>-3.5289</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.995</v>
+        <v>-2.8879</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.641</v>
       </c>
       <c r="G22" t="n">
         <v>-1.5729</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4176</v>
+        <v>0.0419</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6929</v>
+        <v>-0.5857</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2753</v>
+        <v>0.6277</v>
       </c>
       <c r="V22" t="n">
         <v>0.7076</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4629</v>
+        <v>-6.0542</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9108</v>
+        <v>-5.7681</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4479</v>
+        <v>-0.2861</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2979</v>
@@ -2248,13 +2248,13 @@
         <v>1.8731</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3253</v>
+        <v>1.7341</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4098</v>
+        <v>0.5525</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9156</v>
+        <v>1.1816</v>
       </c>
       <c r="V23" t="n">
         <v>0.0071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.307399999999999</v>
+        <v>-6.3076</v>
       </c>
       <c r="E25" t="n">
-        <v>6.298099999999998</v>
+        <v>6.298000000000004</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.6056</v>
+        <v>-12.6055</v>
       </c>
       <c r="G25" t="n">
         <v>-7.368799999999998</v>
@@ -2404,10 +2404,10 @@
         <v>13.5279</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.040700000000001</v>
+        <v>-1.0406</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.6022</v>
+        <v>-1.6023</v>
       </c>
       <c r="U25" t="n">
         <v>0.5616</v>
